--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96173</v>
+        <v>96179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128549992</v>
       </c>
       <c r="B3" t="n">
-        <v>57486</v>
+        <v>57490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128549998</v>
       </c>
       <c r="B4" t="n">
-        <v>56619</v>
+        <v>56623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96179</v>
+        <v>96185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96187</v>
+        <v>96188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128549992</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>57517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128549998</v>
       </c>
       <c r="B4" t="n">
-        <v>56623</v>
+        <v>56650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128549992</v>
       </c>
       <c r="B3" t="n">
-        <v>57517</v>
+        <v>57521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128549998</v>
       </c>
       <c r="B4" t="n">
-        <v>56650</v>
+        <v>56653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128549992</v>
       </c>
       <c r="B3" t="n">
-        <v>57521</v>
+        <v>57524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128549998</v>
       </c>
       <c r="B4" t="n">
-        <v>56653</v>
+        <v>56656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96242</v>
+        <v>96247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96247</v>
+        <v>96255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128549961</v>
       </c>
       <c r="B2" t="n">
-        <v>96255</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128549992</v>
+        <v>128549999</v>
       </c>
       <c r="B3" t="n">
-        <v>57524</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585037</v>
+        <v>585141</v>
       </c>
       <c r="R3" t="n">
-        <v>6318376</v>
+        <v>6318412</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128549998</v>
+        <v>128549992</v>
       </c>
       <c r="B4" t="n">
-        <v>56656</v>
+        <v>57754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208255</v>
+        <v>102118</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585085</v>
+        <v>585037</v>
       </c>
       <c r="R4" t="n">
-        <v>6318381</v>
+        <v>6318376</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,6 +1016,122 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smedmossen solpark NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128549998</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smedmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585085</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6318381</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Smedmossen solpark NVI 2025</t>
         </is>

--- a/artfynd/A 11926-2023 artfynd.xlsx
+++ b/artfynd/A 11926-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549961</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549999</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>